--- a/data/trans_orig/P70C2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P70C2_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le es dificil cumplir con las obligaciones familiares debido al tiempo que paso en el trabajo en 2023</t>
+          <t>Población según si le es dificil cumplir con las obligaciones familiares debido al tiempo que paso en el trabajo en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63879</t>
+          <t>62314</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87666</t>
+          <t>87112</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33418</t>
+          <t>32292</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51132</t>
+          <t>51172</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104134</t>
+          <t>102298</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>134582</t>
+          <t>132728</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>62,4%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22673</t>
+          <t>21739</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43084</t>
+          <t>43127</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9873</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22109</t>
+          <t>22577</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37329</t>
+          <t>35499</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61851</t>
+          <t>60712</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2077</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>11437</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,47 +1006,47 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>10,3%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>10062</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>5703</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>16061</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>2,68%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>10,31%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>10062</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>5815</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>16142</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>6604</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22076</t>
+          <t>21441</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3080</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11091</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28945</t>
+          <t>27587</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>986</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9680</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14395</t>
+          <t>14832</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22855</t>
+          <t>24551</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27376</t>
+          <t>30105</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>628255</t>
+          <t>632836</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1009988</t>
+          <t>1007957</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>443251</t>
+          <t>438762</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>600134</t>
+          <t>602570</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1107752</t>
+          <t>1111145</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1551227</t>
+          <t>1584257</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>68,24%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>149611</t>
+          <t>147271</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>324307</t>
+          <t>326370</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>154621</t>
+          <t>155609</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>232064</t>
+          <t>233586</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>337935</t>
+          <t>325819</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>535938</t>
+          <t>537284</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66401</t>
+          <t>66261</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>153641</t>
+          <t>151771</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59094</t>
+          <t>59061</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96151</t>
+          <t>97760</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133857</t>
+          <t>133152</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>230752</t>
+          <t>233818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73520</t>
+          <t>69564</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>162613</t>
+          <t>160416</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62775</t>
+          <t>61430</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>103623</t>
+          <t>102771</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>148531</t>
+          <t>139835</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>250652</t>
+          <t>249613</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37411</t>
+          <t>37761</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92948</t>
+          <t>91075</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44945</t>
+          <t>42378</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78594</t>
+          <t>78059</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>91604</t>
+          <t>89058</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>159595</t>
+          <t>160057</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20746</t>
+          <t>21118</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57753</t>
+          <t>55897</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12907</t>
+          <t>13057</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28583</t>
+          <t>28178</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41324</t>
+          <t>39936</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78181</t>
+          <t>78576</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>233175</t>
+          <t>232361</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>280776</t>
+          <t>280235</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>216542</t>
+          <t>215787</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>253321</t>
+          <t>251845</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>459096</t>
+          <t>458698</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>521486</t>
+          <t>518717</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,27%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89118</t>
+          <t>89203</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>134668</t>
+          <t>134201</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>86598</t>
+          <t>87465</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>116333</t>
+          <t>117032</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>184873</t>
+          <t>185692</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>240579</t>
+          <t>240124</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17561</t>
+          <t>17547</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38682</t>
+          <t>39757</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23194</t>
+          <t>23249</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40090</t>
+          <t>39802</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44671</t>
+          <t>44614</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72080</t>
+          <t>72903</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18641</t>
+          <t>19435</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42625</t>
+          <t>41998</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24378</t>
+          <t>25173</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>45197</t>
+          <t>44149</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>49717</t>
+          <t>50123</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>80909</t>
+          <t>79171</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11350</t>
+          <t>11525</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34982</t>
+          <t>35086</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19026</t>
+          <t>18605</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36197</t>
+          <t>36694</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34647</t>
+          <t>33264</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65774</t>
+          <t>65718</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17092</t>
+          <t>17578</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>7734</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20854</t>
+          <t>19317</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>13668</t>
+          <t>14222</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>32620</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>970688</t>
+          <t>966293</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1390880</t>
+          <t>1395551</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>717453</t>
+          <t>720889</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>892975</t>
+          <t>881562</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1724843</t>
+          <t>1726882</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2224573</t>
+          <t>2263398</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>66,09%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>262408</t>
+          <t>274062</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>471590</t>
+          <t>474281</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>264503</t>
+          <t>273508</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>350589</t>
+          <t>353078</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>558121</t>
+          <t>541517</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>800046</t>
+          <t>798791</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>93951</t>
+          <t>97318</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>183069</t>
+          <t>180299</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>91851</t>
+          <t>93428</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>133260</t>
+          <t>132792</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>196059</t>
+          <t>199700</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>300863</t>
+          <t>300989</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>109432</t>
+          <t>111994</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>202723</t>
+          <t>205036</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>100352</t>
+          <t>101980</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>145120</t>
+          <t>146422</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>224829</t>
+          <t>224761</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>332232</t>
+          <t>332934</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>56940</t>
+          <t>60147</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>116907</t>
+          <t>119755</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>74725</t>
+          <t>72032</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>114347</t>
+          <t>111741</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>143727</t>
+          <t>140728</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>218890</t>
+          <t>219755</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>32078</t>
+          <t>31854</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>67063</t>
+          <t>68873</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28649</t>
+          <t>27520</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>62198</t>
+          <t>61637</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>67902</t>
+          <t>67713</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>117840</t>
+          <t>117766</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">

--- a/data/trans_orig/P70C2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P70C2_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>75461</t>
+          <t>99805</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62314</t>
+          <t>84394</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87112</t>
+          <t>112799</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42855</t>
+          <t>50374</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32292</t>
+          <t>42411</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51172</t>
+          <t>58296</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>118317</t>
+          <t>150179</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102298</t>
+          <t>132620</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132728</t>
+          <t>165545</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>65,55%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32058</t>
+          <t>36513</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21739</t>
+          <t>26049</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43127</t>
+          <t>49647</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15363</t>
+          <t>16897</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>12074</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22577</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>47421</t>
+          <t>53409</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35499</t>
+          <t>40947</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60712</t>
+          <t>67233</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>7776</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8300</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>10062</t>
+          <t>13112</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>7449</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16061</t>
+          <t>21376</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12366</t>
+          <t>12971</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21441</t>
+          <t>24266</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6241</t>
+          <t>7508</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>13133</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18607</t>
+          <t>20479</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>12086</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27587</t>
+          <t>30368</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9281</t>
+          <t>9756</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4284</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>10280</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>9971</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14832</t>
+          <t>17147</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2497</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24551</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>30105</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>80609</t>
+          <t>88600</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80609</t>
+          <t>88600</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80609</t>
+          <t>88600</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>212712</t>
+          <t>252535</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>212712</t>
+          <t>252535</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>212712</t>
+          <t>252535</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>773832</t>
+          <t>589607</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>632836</t>
+          <t>551548</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1007957</t>
+          <t>627600</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>496858</t>
+          <t>444794</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>438762</t>
+          <t>417397</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>602570</t>
+          <t>473639</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1270689</t>
+          <t>1034401</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1111145</t>
+          <t>986694</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1584257</t>
+          <t>1085437</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>49,07%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>258841</t>
+          <t>299360</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>147271</t>
+          <t>268918</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>326370</t>
+          <t>333030</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>201683</t>
+          <t>227578</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>155609</t>
+          <t>202835</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>233586</t>
+          <t>248611</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>460525</t>
+          <t>526938</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>325819</t>
+          <t>492634</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>537284</t>
+          <t>575995</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>114648</t>
+          <t>127472</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66261</t>
+          <t>103344</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>151771</t>
+          <t>156651</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>77924</t>
+          <t>86768</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59061</t>
+          <t>72506</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97760</t>
+          <t>104441</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>192571</t>
+          <t>214240</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133152</t>
+          <t>184193</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>233818</t>
+          <t>246621</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>124067</t>
+          <t>133010</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69564</t>
+          <t>108685</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>160416</t>
+          <t>162030</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>84058</t>
+          <t>90182</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61430</t>
+          <t>76213</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102771</t>
+          <t>107598</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>208125</t>
+          <t>223192</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>139835</t>
+          <t>195839</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>249613</t>
+          <t>253141</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>68917</t>
+          <t>72933</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37761</t>
+          <t>55963</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>91075</t>
+          <t>90902</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62272</t>
+          <t>70348</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42378</t>
+          <t>56613</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78059</t>
+          <t>87489</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>131189</t>
+          <t>143281</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>89058</t>
+          <t>121951</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>160057</t>
+          <t>166932</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>38829</t>
+          <t>46271</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21118</t>
+          <t>31953</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55897</t>
+          <t>62554</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19822</t>
+          <t>23715</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13057</t>
+          <t>15965</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28178</t>
+          <t>32775</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>58651</t>
+          <t>69986</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39936</t>
+          <t>54764</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78576</t>
+          <t>88419</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1379134</t>
+          <t>1268653</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1379134</t>
+          <t>1268653</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1379134</t>
+          <t>1268653</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>942616</t>
+          <t>943384</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>942616</t>
+          <t>943384</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>942616</t>
+          <t>943384</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2321750</t>
+          <t>2212037</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2321750</t>
+          <t>2212037</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2321750</t>
+          <t>2212037</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,69 +2315,69 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>257653</t>
+          <t>282058</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>232361</t>
+          <t>257763</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>280235</t>
+          <t>306225</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>57,37%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>52,43%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>62,29%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>256567</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>237107</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>275983</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>53,16%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>49,13%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
           <t>57,18%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>51,57%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>62,19%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>234184</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>215787</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>251845</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>53,28%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>49,09%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>57,3%</t>
-        </is>
-      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>575</t>
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>491838</t>
+          <t>538625</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>458698</t>
+          <t>507971</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>518717</t>
+          <t>569022</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>58,4%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>108538</t>
+          <t>113912</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89203</t>
+          <t>94644</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>134201</t>
+          <t>133653</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>101007</t>
+          <t>109531</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>87465</t>
+          <t>94437</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>117032</t>
+          <t>124911</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>209545</t>
+          <t>223443</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>185692</t>
+          <t>200904</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>240124</t>
+          <t>251215</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>26789</t>
+          <t>28526</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17547</t>
+          <t>18768</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39757</t>
+          <t>42443</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>30797</t>
+          <t>33884</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23249</t>
+          <t>24827</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39802</t>
+          <t>44201</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>57586</t>
+          <t>62410</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44614</t>
+          <t>49689</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72903</t>
+          <t>79716</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29290</t>
+          <t>33803</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19435</t>
+          <t>22106</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41998</t>
+          <t>47515</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>33974</t>
+          <t>39306</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25173</t>
+          <t>28994</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>44149</t>
+          <t>51014</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>63264</t>
+          <t>73109</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>50123</t>
+          <t>57015</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>79171</t>
+          <t>91614</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>19428</t>
+          <t>22428</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11525</t>
+          <t>12281</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35086</t>
+          <t>36360</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>26860</t>
+          <t>29271</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18605</t>
+          <t>21528</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36694</t>
+          <t>40688</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>46288</t>
+          <t>51699</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33264</t>
+          <t>38587</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65718</t>
+          <t>72623</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8897</t>
+          <t>10919</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17578</t>
+          <t>20916</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>12720</t>
+          <t>14068</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19317</t>
+          <t>21837</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>21617</t>
+          <t>24988</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14222</t>
+          <t>16858</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32620</t>
+          <t>37705</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>450594</t>
+          <t>491647</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>450594</t>
+          <t>491647</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>450594</t>
+          <t>491647</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>439543</t>
+          <t>482627</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>439543</t>
+          <t>482627</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>439543</t>
+          <t>482627</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>890138</t>
+          <t>974274</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>890138</t>
+          <t>974274</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>890138</t>
+          <t>974274</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1106946</t>
+          <t>971470</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>966293</t>
+          <t>924185</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1395551</t>
+          <t>1017286</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>773898</t>
+          <t>751736</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>720889</t>
+          <t>712168</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>881562</t>
+          <t>784358</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1880844</t>
+          <t>1723205</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1726882</t>
+          <t>1664019</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2263398</t>
+          <t>1780068</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>51,76%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>399438</t>
+          <t>449784</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>274062</t>
+          <t>406716</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>474281</t>
+          <t>492277</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>318053</t>
+          <t>354006</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>273508</t>
+          <t>322734</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>353078</t>
+          <t>382491</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>717491</t>
+          <t>803790</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>541517</t>
+          <t>754881</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>798791</t>
+          <t>849296</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>147073</t>
+          <t>163774</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>97318</t>
+          <t>136012</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>180299</t>
+          <t>193340</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>113146</t>
+          <t>125988</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>93428</t>
+          <t>109545</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>132792</t>
+          <t>146033</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>260219</t>
+          <t>289762</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>199700</t>
+          <t>254206</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>300989</t>
+          <t>326053</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>165723</t>
+          <t>179784</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>111994</t>
+          <t>151967</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>205036</t>
+          <t>210387</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>124273</t>
+          <t>136996</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>101980</t>
+          <t>119055</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>146422</t>
+          <t>158360</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>289996</t>
+          <t>316780</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>224761</t>
+          <t>281288</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>332934</t>
+          <t>351725</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>92429</t>
+          <t>99594</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>60147</t>
+          <t>80962</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>119755</t>
+          <t>124101</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>93416</t>
+          <t>105357</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>72032</t>
+          <t>87891</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>111741</t>
+          <t>125684</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>185845</t>
+          <t>204951</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>140728</t>
+          <t>181242</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>219755</t>
+          <t>235513</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>50223</t>
+          <t>59829</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31854</t>
+          <t>43981</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>68873</t>
+          <t>78925</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>39982</t>
+          <t>40529</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>30862</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>61637</t>
+          <t>53073</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>90205</t>
+          <t>100357</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>67713</t>
+          <t>82069</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>117766</t>
+          <t>122825</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1961831</t>
+          <t>1924235</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1961831</t>
+          <t>1924235</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1961831</t>
+          <t>1924235</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1462769</t>
+          <t>1514612</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1462769</t>
+          <t>1514612</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1462769</t>
+          <t>1514612</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>3424600</t>
+          <t>3438846</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3424600</t>
+          <t>3438846</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3424600</t>
+          <t>3438846</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
